--- a/annotation/excel/adesanym_annotation.xlsx
+++ b/annotation/excel/adesanym_annotation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="initial" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reannotation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="initial" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="reannotation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'initial'!$A$1:$J$351</definedName>
@@ -525,7 +525,11 @@
           <t>Whatever hotel you booked me at. The reference number is: GXQZCBL8</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -537,7 +541,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -565,7 +573,11 @@
           <t>its ok. book for 8 people and help me get the reference number please</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -577,7 +589,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -605,7 +621,11 @@
           <t>Yes, that would be great. I would like my check-in to be on Saturday. I will be staying for 2 nights and there will be a total of 5 people.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -617,7 +637,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -645,7 +669,11 @@
           <t>Thank you. That's all I needed.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -685,7 +713,11 @@
           <t>Yes, I'll also need a taxi that will take me between the two places. I'll need to arrive at the restaurant by 15:00.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -697,7 +729,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -725,7 +761,11 @@
           <t>I have no preference. can i please have the address and phone number of one of them ?</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -765,7 +805,11 @@
           <t>What time does the train arrive in Bishops Stortford? I also am looking for a place to stay that is 3 stars and in the moderate range.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -777,7 +821,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -805,7 +853,11 @@
           <t>Yes please make a booking for 8 people at 12:30 on friday.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -817,7 +869,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -845,7 +901,11 @@
           <t>Is Bridge Guest House in the south? If so, I will also need a taxi to take me from the restaurant to the guesthouse.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -885,7 +945,11 @@
           <t>I would like to go to London Liverpool Street. Could you check the price for me?</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -925,7 +989,11 @@
           <t>I would like to leave on Saturday.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -965,7 +1033,11 @@
           <t>Is there an italian restaurant in the south part of town?</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1005,7 +1077,11 @@
           <t>I would like to leave after 12:30 please.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1017,7 +1093,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1045,7 +1125,11 @@
           <t>I'm leaving from Peterborough.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1057,7 +1141,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1085,7 +1173,11 @@
           <t>No that's all I needed with that. i also need a train leaving after 12:15 heading to kings lynn.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1125,7 +1217,11 @@
           <t>Yes, how about moderately priced places to stay with 4 stars in the North? I also need free parking.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1137,7 +1233,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1165,7 +1265,11 @@
           <t>Thanks, I also need to train form broxbourne to cambridge on sunday.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1177,7 +1281,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1205,7 +1313,11 @@
           <t>Yes, one more thing. We need a taxi that will take us from Clare Hall to our guesthouse.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1217,7 +1329,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1245,7 +1361,11 @@
           <t>I would like Chinese food.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1285,7 +1405,11 @@
           <t>Much later, I can't leave any earlier than 16:15.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1325,7 +1449,11 @@
           <t>Nothing specific. Can you make a recommendation and give me their address, postcode, and entrance fee?</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1365,7 +1493,11 @@
           <t>Thank you. What is the postcode?</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1405,7 +1537,11 @@
           <t>yes for 2 nights starting thursday</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1417,7 +1553,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1445,7 +1585,11 @@
           <t>Thats all thank you for your help,goodbye</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1485,7 +1629,11 @@
           <t>Um, how about the address too please?</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1525,7 +1673,11 @@
           <t>Thank you! I also am looking for a place to eat at in the west area. I would prefer a nice expensive one.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1537,7 +1689,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1565,7 +1721,11 @@
           <t>thanks you very much</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1605,7 +1765,11 @@
           <t>I'd like to check in on Friday for 4 nights. Book it for 5 people.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1617,7 +1781,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1645,7 +1813,11 @@
           <t>I'm sorry my taxi has already been booked. Thank you for your help.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1657,7 +1829,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1685,7 +1861,11 @@
           <t>Thank you for the help!</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1725,7 +1905,11 @@
           <t>can you tell me how much the entrance fee is?</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1765,7 +1949,11 @@
           <t>Nope, that should be everything. Thank you so much for all of your help.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1805,7 +1993,11 @@
           <t>No, I'm going to have my car with me so I can get to any part of town. But now that I think of it, I'd like to have free parking.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1817,7 +2009,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1845,7 +2041,11 @@
           <t>What about the phone number?</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1885,7 +2085,11 @@
           <t>Thanks so much. I am also wanting to see if you can help me find a cheap room to stay in.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1897,7 +2101,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1925,7 +2133,11 @@
           <t>Yes, can you please find me a good Indian restaurant in the same area as the attraction? Money is no object.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -1965,7 +2177,11 @@
           <t>Pick one of the best churches for me and let me know the entrance fee please.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2005,7 +2221,11 @@
           <t>From the cambridge belfry to chiquito restaurant bar. We won't be fit to drive!</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2045,7 +2265,11 @@
           <t>Thank you that will be all I need today?</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2085,7 +2309,11 @@
           <t>No, thank you. I'd just like to have the information for now.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2125,7 +2353,11 @@
           <t>I'm sorry, I said I needed a seat for me, but I actually need 7 seats total. My friends would not be happy if I stranded them.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2165,7 +2397,11 @@
           <t>I will be departing from London Kings Cross.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2177,7 +2413,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2205,7 +2445,11 @@
           <t>what is its departure time?</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2245,7 +2489,11 @@
           <t>That will be all for today. Thanks. Goodbye</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2285,7 +2533,11 @@
           <t>Yeah that's okay. Please book it for 2 people and 3 nights starting Sunday.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2297,7 +2549,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2325,7 +2581,11 @@
           <t>Thanks, I'm all set now. Take care!</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2365,7 +2625,11 @@
           <t>I prefer the south part of town if you have anything.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2405,7 +2669,11 @@
           <t>I will be departing from 3 towns over.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2417,7 +2685,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2445,7 +2717,11 @@
           <t>Can you check for a different hotel in the same pricerange?</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2485,7 +2761,11 @@
           <t>I'll go with the expensive one. Can you book me a room for 8 people, 2 nights on Sunday please?</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2525,7 +2805,11 @@
           <t>No, thank you. That's all I needed today.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2565,7 +2849,11 @@
           <t>I am looking for a train that will depart from Norwich on Sunday</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2577,7 +2865,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2605,7 +2897,11 @@
           <t>Yes, that would be great!</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2645,7 +2941,11 @@
           <t>No that is all. Goodbye</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2685,7 +2985,11 @@
           <t>I think Chinese may have caught my attention.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2725,7 +3029,11 @@
           <t>I'd like a room in the north please</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2765,7 +3073,11 @@
           <t>How about Chinese food on the east part of town?</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2777,7 +3089,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2805,7 +3121,11 @@
           <t>I'm good, that's all I needed, Thanks!</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2845,7 +3165,11 @@
           <t>No, could you recommend me a place? I'm looking for to book a table for 2 on Thursday at 11:30.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2885,7 +3209,11 @@
           <t>What is their address?</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2925,7 +3253,11 @@
           <t>Sure. What is the entrance fee and phone number?</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -2937,7 +3269,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2965,7 +3301,11 @@
           <t>I really need a guesthouse can you find one for me please?</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3005,7 +3345,11 @@
           <t>Yes please; I'd greatly prefer the moderate price range as I'm on a bit of a budget.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3017,7 +3361,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3045,7 +3393,11 @@
           <t>Yes I am looking for a Train that departs from Cambridge and arrives at Birmingham New Street.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3057,7 +3409,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3085,7 +3441,11 @@
           <t>I'd like to find a restaurant called Cotto, please.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3125,7 +3485,11 @@
           <t>Yes, I would like their address please.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3137,7 +3501,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3165,7 +3533,11 @@
           <t>Yes, can you please and send me the reference number?</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3177,7 +3549,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3205,7 +3581,11 @@
           <t>Great, thanks so much!</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3245,7 +3625,11 @@
           <t>I also need a taxi between the two places.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3257,7 +3641,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3285,7 +3673,11 @@
           <t>I would like the taxi arrives at the restaurant by 13:30. Also could you provide me with the phone number for Castle Galleries?</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3297,7 +3689,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3325,7 +3721,11 @@
           <t>In the west please, I am open to suggestions just let me know what the postcode, entrance fee a number are.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3337,7 +3737,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3365,7 +3769,11 @@
           <t>Alright, that's everything! Thank you very much.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3405,7 +3813,11 @@
           <t>actually, i want chinese food.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3417,7 +3829,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/0/0/4).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3445,7 +3861,11 @@
           <t>Thank you, that will be all.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3485,7 +3905,11 @@
           <t>I need to be at the restaurant at 11:30.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3497,7 +3921,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3525,7 +3953,11 @@
           <t>What is the price on that train?</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3565,7 +3997,11 @@
           <t>Perfect. I will need tickets for 6 people. Please provide the reference number.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3577,7 +4013,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3605,7 +4045,11 @@
           <t>I don't have a preference. I do need the area, address and postcode.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3617,7 +4061,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3645,7 +4093,11 @@
           <t>I'd prefer a hotel, rather than a guesthouse.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3685,7 +4137,11 @@
           <t>That will be great. Can you book me 8 tickets please?</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3725,7 +4181,11 @@
           <t>Thank you. I also want a train for friday, from broxbourne to cambridge</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3737,7 +4197,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3765,7 +4229,11 @@
           <t>I will have a party of 4 people.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3777,7 +4245,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3805,7 +4277,11 @@
           <t>That will work. Please book 8 tickets. I'll also need a reference number.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3817,7 +4293,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3845,7 +4325,11 @@
           <t>I would like Mexican, I would need a table for 6 at 16:00 on Monday</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3885,7 +4369,11 @@
           <t>No, thank you. Goodbye.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3925,7 +4413,11 @@
           <t>I'd like a booking for Meghna for 5 people at 10:45 on the same day, please. And include the reference number.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -3937,7 +4429,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3965,7 +4461,11 @@
           <t>Nope, that was everything, thank you very much!</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4005,7 +4505,11 @@
           <t>Cmabridge to Norwich.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4017,7 +4521,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4045,7 +4553,11 @@
           <t>Great. Please book it for 8 people and 4 nights starting from Monday.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4057,7 +4569,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4085,7 +4601,11 @@
           <t>Yes please.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4097,7 +4617,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4125,7 +4649,11 @@
           <t>Yes it is the carolina bed and breakfast.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4165,7 +4693,11 @@
           <t>Bummer, are there any nightclubs in the city centre instead?</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4205,7 +4737,11 @@
           <t>I would also like some Italian food in the area.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4217,7 +4753,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4245,7 +4785,11 @@
           <t>Yes please 6 people, at 14:45 on Thursday.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4257,7 +4801,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4285,7 +4833,11 @@
           <t>That is all thank you goodbye.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4325,7 +4877,11 @@
           <t>I want to leave the hotel at 22:45.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4365,7 +4921,11 @@
           <t>ok thanks, byeeee</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4405,7 +4965,11 @@
           <t>Yes, that would be fine. I need to make the booking for 8 people, please.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4417,7 +4981,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4445,7 +5013,11 @@
           <t>I also need a place to eat.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4457,7 +5029,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4485,7 +5061,11 @@
           <t>Please book Alexander Bed and Breakfast for 4 people and 5 nights starting on Tuesday.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4497,7 +5077,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4525,7 +5109,11 @@
           <t>no, thank you. Goodbye.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4565,7 +5153,11 @@
           <t>I am headed to curry prince.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4577,7 +5169,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4605,7 +5201,11 @@
           <t>Any area is fine. Do you have a favorite? Maybe we can check that one out. Which one do you like?</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4645,7 +5245,11 @@
           <t>I will be departing from Bishops Stortford on Sunday.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4685,7 +5289,11 @@
           <t>Thank you so much for your help today.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4725,7 +5333,11 @@
           <t>Great, thank you. Could you also help me with booking a taxi to go from the hotel to the cinema?</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4737,7 +5349,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4765,7 +5381,11 @@
           <t>I need also a taxi to leave the hotel by 2:30</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4805,7 +5425,11 @@
           <t>No thank you that will be all</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4845,7 +5469,11 @@
           <t>I will. Thanks again. Good-bye.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4885,7 +5513,11 @@
           <t>No, that's all I need for today. Good bye.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4925,7 +5557,11 @@
           <t>Yes, the same party. I'd like the reservation for 10:00 that same Tuesday.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -4937,7 +5573,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4965,7 +5605,11 @@
           <t>Is there a entrance fee?</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5005,7 +5649,11 @@
           <t>Thank you that's all I need today.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5045,7 +5693,11 @@
           <t>That sounds good. Can I get the address and postcode, please?</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5057,7 +5709,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5085,7 +5741,11 @@
           <t>leaves at 1900hrs, arrives on sunday and booked fir one person.get me the reference number too</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5097,7 +5757,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5125,7 +5789,11 @@
           <t>Yes, that works. May i have the address?</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5165,7 +5833,11 @@
           <t>I would like to arrive in Cambridge by 15:00, please.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5177,7 +5849,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5205,7 +5881,11 @@
           <t>Great. I'm not ready to book today though. I am also looking for a place to stay.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5217,7 +5897,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5245,7 +5929,11 @@
           <t>Does the Aylesbury have free wifi?</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5285,7 +5973,11 @@
           <t>I will. Thanks for your help.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5325,7 +6017,11 @@
           <t>I would like my stay to begin on Tuesday.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5365,7 +6061,11 @@
           <t>Which of those have free wifi?</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5405,7 +6105,11 @@
           <t>No, I really don't mind. Recommend one to me.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5445,7 +6149,11 @@
           <t>No. Just as I make my arrival time but not leave unnecessarily early.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5485,7 +6193,11 @@
           <t>I am looking for a hotel in the same area that has free parking.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5497,7 +6209,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5525,7 +6241,11 @@
           <t>Bummer. I could try Chinese. Is there anything in the north?</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5565,7 +6285,11 @@
           <t>It will just be me, so one.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5577,7 +6301,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5605,7 +6333,11 @@
           <t>Okay thanks. That's all for now. Bye.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5645,7 +6377,11 @@
           <t>I would also like to eat somewhere cheap in the middle of town.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5657,7 +6393,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5685,7 +6425,11 @@
           <t>I'd like to book a table for the same number of people (5) for that same day at 16:15 if it's available. I'd also like the reference number for that please.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5697,7 +6441,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5725,7 +6473,11 @@
           <t>yes, please for 3 people for 3 nights starting on saturday</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5737,7 +6489,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5765,7 +6521,11 @@
           <t>Thank, I also want to dine at a restaurant in the same area with an expensive price range.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5805,7 +6565,11 @@
           <t>Yes, how about North American food. I will also need the address, phone number, and postcode.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5817,7 +6581,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5845,7 +6613,11 @@
           <t>I would like one located in the east with a moderate price range.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5885,7 +6657,11 @@
           <t>Thank you very much! Can you also help me find a train? I am looking for one that leaves from Cambridge after 11:00 and goes to Kings Lynn on Friday.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5897,7 +6673,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5925,7 +6705,11 @@
           <t>Thank you very much.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -5965,7 +6749,11 @@
           <t>I need to depart from ely and arrive by 16:30.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6005,7 +6793,11 @@
           <t>Yes, that would be find. I'll need to book tickets for 7 people. Can I have the reference number please?</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6045,7 +6837,11 @@
           <t>No, that's it. Thank you. Goodbye.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6085,7 +6881,11 @@
           <t>Sorry, I want to leave after 14:30. Please let me know the time of arrival and travel time.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6097,7 +6897,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -6125,7 +6929,11 @@
           <t>No thank you for all your help.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6165,7 +6973,11 @@
           <t>Sure. Check only for hotels which include free parking also.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6177,7 +6989,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -6205,7 +7021,11 @@
           <t>Oops look like I made a typo. Is that hotel a guesthouse and in the cheap price range?</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6217,7 +7037,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6245,7 +7069,11 @@
           <t>Yes, that sounds great. I would like to book the train for 7 people. What is the reference number?</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6285,7 +7113,11 @@
           <t>Thanks! I also need a train after 14:45 on Saturday.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6297,7 +7129,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6325,7 +7161,11 @@
           <t>Can I book it for 1 person at 14:15 on thursday?</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6365,7 +7205,11 @@
           <t>Yes please, go ahead and book that.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6377,7 +7221,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6405,7 +7253,11 @@
           <t>No, I'd like that zero star cheap guesthouse in the north.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6445,7 +7297,11 @@
           <t>Book it for 3 people.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6457,7 +7313,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6485,7 +7345,11 @@
           <t>No, that is all I need today. Thank you so much.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6525,7 +7389,11 @@
           <t>How about 4 nights instead of 5?</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6537,7 +7405,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6565,7 +7437,11 @@
           <t>I do, yes. I would like to stay in the center of town. I need it to fit five people, for 3 nights, starting Wednesday afternoon.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6577,7 +7453,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6605,7 +7485,11 @@
           <t>How about vietnamese food?</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6645,7 +7529,11 @@
           <t>I also need a train from broxbourne.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6657,7 +7545,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6685,7 +7577,11 @@
           <t>I would like to reserve it for 11:15 for 8 people.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6725,7 +7621,11 @@
           <t>I am also looking for information on Clare College.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6737,7 +7637,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6765,7 +7669,11 @@
           <t>That sounds good. Where is it located? I was looking for somewhere in the east.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6805,7 +7713,11 @@
           <t>I would like the taxi to leave the restaurant by 14:45.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6845,7 +7757,11 @@
           <t>That will be all, thank you. Have a great day.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6885,7 +7801,11 @@
           <t>Alright, thanks for the information. That was all I needed for today.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6925,7 +7845,11 @@
           <t>That was all the information I needed, thank you.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -6965,7 +7889,11 @@
           <t>How about a theater in the south?</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7005,7 +7933,11 @@
           <t>I'll be leaving monday and the departure time doesn't matter.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7045,7 +7977,11 @@
           <t>I will also need a train on Tuesday.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7085,7 +8021,11 @@
           <t>Can I get their phone number please?</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7125,7 +8065,11 @@
           <t>Do they have internet and if so what is the address there?</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7165,7 +8109,11 @@
           <t>Thank you, goodbye</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7205,7 +8153,11 @@
           <t>Yes, and please be sure to give me the ID.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7217,7 +8169,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -7245,7 +8201,11 @@
           <t>Thanks. Can you provide the phone number and postcode too?</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7285,7 +8245,11 @@
           <t>Can you give me some additional information on the Asian Oriental one?</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7325,7 +8289,11 @@
           <t>We would like to try a Portuguese place. Is there one available?</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7365,7 +8333,11 @@
           <t>Yes, please. Same people, date, and time.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7377,7 +8349,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -7405,7 +8381,11 @@
           <t>No it will be for 2 people for 5 nights.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7445,7 +8425,11 @@
           <t>No, thank you, I am all set.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7485,7 +8469,11 @@
           <t>Great! May I get the phone number and address?</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7525,7 +8513,11 @@
           <t>Sure, let's try modern English food.</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7565,7 +8557,11 @@
           <t>I prefer to stay somewhere in the cheap price range, and it should include free parking.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7577,7 +8573,11 @@
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7605,7 +8605,11 @@
           <t>That sounds interesting. Could you give me the address?</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7645,7 +8649,11 @@
           <t>No, that will be all. Thank you.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7685,7 +8693,11 @@
           <t>Yes - I'm looking for a 3-star place to stay. Something moderately priced.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7697,7 +8709,11 @@
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -7725,7 +8741,11 @@
           <t>Thank you, that was all I needed today. Goodbye.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7765,7 +8785,11 @@
           <t>That will be everything I needed today. Thanks for your help!</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7805,7 +8829,11 @@
           <t>What is the total travel time for the train?</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7845,7 +8873,11 @@
           <t>No, that's all thank you very much. Goodbye</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7885,7 +8917,11 @@
           <t>Yes, I'm looking for something in the west.</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7925,7 +8961,11 @@
           <t>That's all, thanks</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -7965,7 +9005,11 @@
           <t>Thanks so much, that sounds perfect.</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8005,7 +9049,11 @@
           <t>No thanks, just needed the address. That's all for today thank you!</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8017,7 +9065,11 @@
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
-      <c r="J189" s="2" t="inlineStr"/>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -8045,7 +9097,11 @@
           <t>Thank you! I think that is all I need for today.</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8085,7 +9141,11 @@
           <t>How about a museum instead?</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8097,7 +9157,11 @@
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
-      <c r="J191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8125,7 +9189,11 @@
           <t>Nope, that takes care of all my needs! Thanks, goodbye!</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8165,7 +9233,11 @@
           <t>I'd just like the travel time and train ID for that one please.</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8177,7 +9249,11 @@
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" s="2" t="inlineStr"/>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -8205,7 +9281,11 @@
           <t>No thanks. I also need an expensive place to stay that has free parking.</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8217,7 +9297,11 @@
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" s="2" t="inlineStr"/>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -8245,7 +9329,11 @@
           <t>no, thanks for all of your help you have been great!</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8285,7 +9373,11 @@
           <t>No, I think that covers everything. Thanks!</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8325,7 +9417,11 @@
           <t>book one that arrives by 10:15 and goes to cambridge</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8337,7 +9433,11 @@
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="2" t="inlineStr"/>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -8365,7 +9465,11 @@
           <t>Alright, all I need the travel time and that should be all, thanks!</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8377,7 +9481,11 @@
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected SOCIAL via tie break order (scores C/A/R/I/S=0/0/2/2/4).</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -8405,7 +9513,11 @@
           <t>Does that place have free wifi?</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8417,7 +9529,11 @@
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -8445,7 +9561,11 @@
           <t>it's called gonville and caius college.</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8457,7 +9577,11 @@
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
-      <c r="J200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -8485,7 +9609,11 @@
           <t>Thanks so much. Can you help me find a place to stay in that area as well?</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8525,7 +9653,11 @@
           <t>I would maybe be interested in booking this train. What is the train id, price per ticket and arrival time?</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8537,7 +9669,11 @@
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8565,7 +9701,11 @@
           <t>That was everything I needed. Thank you very much for helping me.</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8605,7 +9745,11 @@
           <t>Can you confirm if this hotel is 4 star? If so, I will need to book it for 1 person for five nights starting on wednesday.</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8645,7 +9789,11 @@
           <t>I would like to depart from Cambridge, and travel to Bishops Stortford.</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8657,7 +9805,11 @@
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
-      <c r="J205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -8685,7 +9837,11 @@
           <t>Yes, for the same group of people on Monday at 17:15, please.</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8697,7 +9853,11 @@
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -8725,7 +9885,11 @@
           <t>I would like the earliest train available please. Can you tell me the train ID and travel time please?</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8765,7 +9929,11 @@
           <t>No, that is all. Goodbye!</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8805,7 +9973,11 @@
           <t>That sounds interesting. What part of town is it in?</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8845,7 +10017,11 @@
           <t>Yes what is the address for the business?</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8885,7 +10061,11 @@
           <t>Yes, the address, phone number, and their price range please.</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8897,7 +10077,11 @@
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8925,7 +10109,11 @@
           <t>Any location is fine, but I would prefer something that is in the expensive price range.</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8937,7 +10125,11 @@
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8965,7 +10157,11 @@
           <t>Yes, please find any museums in the town centre.</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -8977,7 +10173,11 @@
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
-      <c r="J213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -9005,7 +10205,11 @@
           <t>italian food please. phone number and postcode please.</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9045,7 +10249,11 @@
           <t>That's okay, can you tell me about parks in town?</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9085,7 +10293,11 @@
           <t>The train should go to peterborough and should leave on monday after 10:30.</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9125,7 +10337,11 @@
           <t>Thank you for all your help today! Goodbye</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9165,7 +10381,11 @@
           <t>That will be all, thank you.</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9205,7 +10425,11 @@
           <t>I'm flexible on the price point butthe place will need to be a guesthouse that also had free wifi.</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9245,7 +10469,11 @@
           <t>Well, can I get some african food instead?</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9257,7 +10485,11 @@
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
-      <c r="J220" s="2" t="inlineStr"/>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -9285,7 +10517,11 @@
           <t>A 2 star would be good. I don't care about price range.</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9297,7 +10533,11 @@
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="2" t="inlineStr"/>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -9325,7 +10565,11 @@
           <t>I need the hotel for four nights, and eight people please.</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9337,7 +10581,11 @@
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="2" t="inlineStr"/>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -9365,7 +10613,11 @@
           <t>Does that arrive before 8:45?</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9377,7 +10629,11 @@
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
-      <c r="J223" s="2" t="inlineStr"/>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9405,7 +10661,11 @@
           <t>Yes please. I've heard that Emmanuel College is an interesting place. What can you tell me about it?</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9445,7 +10705,11 @@
           <t>Yes, can I get the postcode?</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9485,7 +10749,11 @@
           <t>train. The train should be on the same day as the restaurant booking and should go to cambridge</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9497,7 +10765,11 @@
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
-      <c r="J226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9525,7 +10797,11 @@
           <t>Thanks so much, that's all I need today!</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9565,7 +10841,11 @@
           <t>Are there European types of restaurants?</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9605,7 +10885,11 @@
           <t>Can I just get the contact information for La Mimosa for right now?</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9617,7 +10901,11 @@
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
-      <c r="J229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -9645,7 +10933,11 @@
           <t>The train should leave after 17:15 and should go to bishops stortford.</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9685,7 +10977,11 @@
           <t>Is the restaurant in the expensive price range?</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9725,7 +11021,11 @@
           <t>That's all that I need.</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9737,7 +11037,11 @@
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
-      <c r="J232" s="2" t="inlineStr"/>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -9765,7 +11069,11 @@
           <t>Please book for 2 nights, for 1 person starting on Monday.</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9777,7 +11085,11 @@
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -9805,7 +11117,11 @@
           <t>Could you try to book that again for 5 people at 18:00 on Tuesday?</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9845,7 +11161,11 @@
           <t>Umm, no I am going to Leicester from Cambridge on Thursday arriving by 10:15.</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9885,7 +11205,11 @@
           <t>No, that is all I need. Thank you!</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9925,7 +11249,11 @@
           <t>I am leaving Thursday from Birmingham New Street to Cambridge. I want to leave around 11:45.</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9965,7 +11293,11 @@
           <t>I would prefer it be the earliest train you can book.</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -9977,7 +11309,11 @@
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
-      <c r="J238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -10005,7 +11341,11 @@
           <t>What is the price?</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10045,7 +11385,11 @@
           <t>No, can you find another one please?</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10057,7 +11401,11 @@
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
-      <c r="J240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=3/0/4/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -10085,7 +11433,11 @@
           <t>i want to go to rosa's bed and breakfast and would like to arrive by 3</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10125,7 +11477,11 @@
           <t>That's where I am leaving from. I'll need tickets for 3 people and we need to leave after 15:30.</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10137,7 +11493,11 @@
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
-      <c r="J242" s="2" t="inlineStr"/>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -10165,7 +11525,11 @@
           <t>No. I am all set. Thanks. Goodbye.</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10205,7 +11569,11 @@
           <t>I will be departing from stansted airport and want to leave after 18:15.</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10245,7 +11613,11 @@
           <t>yes four people for Friday at 17:30</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10257,7 +11629,11 @@
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
-      <c r="J245" s="2" t="inlineStr"/>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -10285,7 +11661,11 @@
           <t>That's it. Thank you!</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10325,7 +11705,11 @@
           <t>Thanks, I need the phone number too please.</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10337,7 +11721,11 @@
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
-      <c r="J247" s="2" t="inlineStr"/>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -10365,7 +11753,11 @@
           <t>Yes please book it for me.</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr"/>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10377,7 +11769,11 @@
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
-      <c r="J248" s="2" t="inlineStr"/>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10405,7 +11801,11 @@
           <t>Thank you so much that is all I need.</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr"/>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10445,7 +11845,11 @@
           <t>That won't be necessary, I will just need their address and phone number please.</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10485,7 +11889,11 @@
           <t>Can you book a room for 2 people for 2 nights starting on Sunday?</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10525,7 +11933,11 @@
           <t>no thanks that's all</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10565,7 +11977,11 @@
           <t>I's like to depart after 16:15. I just need information, not a booking.</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10577,7 +11993,11 @@
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -10605,7 +12025,11 @@
           <t>Thanks! what is the entrance fee?</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10617,7 +12041,11 @@
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
-      <c r="J254" s="2" t="inlineStr"/>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -10645,7 +12073,11 @@
           <t>Darn, alright. Can we search chinese instead then please?</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10657,7 +12089,11 @@
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
-      <c r="J255" s="2" t="inlineStr"/>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/4).</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -10685,7 +12121,11 @@
           <t>Please reserve for 8 people.</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10697,7 +12137,11 @@
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" s="2" t="inlineStr"/>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -10725,7 +12169,11 @@
           <t>yes, please. For 6 people for 3 nights starting on friday.</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10737,7 +12185,11 @@
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
-      <c r="J257" s="2" t="inlineStr"/>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -10765,7 +12217,11 @@
           <t>No, that will be all. Thank you for your help!</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10805,7 +12261,11 @@
           <t>That is all I needed thank you.</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10845,7 +12305,11 @@
           <t>That is alright. Actually, that should be all I need today. Thank you for your help. Goodbye.</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10857,7 +12321,11 @@
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="2" t="inlineStr"/>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/0/2/4).</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -10885,7 +12353,11 @@
           <t>Yes please. I would like something in the expensive price range.</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10897,7 +12369,11 @@
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr"/>
-      <c r="J261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -10925,7 +12401,11 @@
           <t>Any church will be fine. Can you give me the phone number of one?</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10965,7 +12445,11 @@
           <t>I don't really have a preference, so which one do you think is best?</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -10977,7 +12461,11 @@
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
-      <c r="J263" s="2" t="inlineStr"/>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11005,7 +12493,11 @@
           <t>I'm also looking for a particular hotel - hobsons house. Can you help me with this?</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11017,7 +12509,11 @@
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
-      <c r="J264" s="2" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -11045,7 +12541,11 @@
           <t>Carolina Bed and Breakfast sounds nice. Could I have it booked for 6 people for 4 nights starting on monday?</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11057,7 +12557,11 @@
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
-      <c r="J265" s="2" t="inlineStr"/>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -11085,7 +12589,11 @@
           <t>I will need 6 tickets.</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11097,7 +12605,11 @@
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
-      <c r="J266" s="2" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -11125,7 +12637,11 @@
           <t>okay goodbye</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11165,7 +12681,11 @@
           <t>Don't you have one that serves south african food?</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11177,7 +12697,11 @@
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
-      <c r="J268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -11205,7 +12729,11 @@
           <t>Thanks for your help, that's all I need today!</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11245,7 +12773,11 @@
           <t>Sounds great. Make a reservation for 4 on Friday at 11:00.</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11257,7 +12789,11 @@
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
-      <c r="J270" s="2" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11285,7 +12821,11 @@
           <t>It doesn't matter. I need free parking and prefer a place with 4 stars.</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11325,7 +12865,11 @@
           <t>Great. Thank you very much for your help today. That is all.</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11365,7 +12909,11 @@
           <t>I'd like to book it. Can you book it starting Sunday night for 5 nights. I need reservations for 6 people.</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11377,7 +12925,11 @@
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
-      <c r="J273" s="2" t="inlineStr"/>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -11405,7 +12957,11 @@
           <t>I would also like a train leaving from Cambridge.</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11417,7 +12973,11 @@
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
-      <c r="J274" s="2" t="inlineStr"/>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -11445,7 +13005,11 @@
           <t>Yes, I would like to book a stay for 1 person, starting Monday and for 5 nights.</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11457,7 +13021,11 @@
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
-      <c r="J275" s="2" t="inlineStr"/>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -11485,7 +13053,11 @@
           <t>I need to book a taxi to commute between the museum and the restaurant, leaving the museum by 14:30.</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11497,7 +13069,11 @@
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr"/>
-      <c r="J276" s="2" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -11525,7 +13101,11 @@
           <t>No it doesn't matter, what do you recommend?</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11565,7 +13145,11 @@
           <t>Well I want a hotel not food.</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11577,7 +13161,11 @@
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr"/>
-      <c r="J278" s="2" t="inlineStr"/>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -11605,7 +13193,11 @@
           <t>Can you please book me a table at the restaurant for 2 people?</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr"/>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11645,7 +13237,11 @@
           <t>How about an expensive one. What are my choices in that range?</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr"/>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11685,7 +13281,11 @@
           <t>No that is it. Thank you so much.</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr"/>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11725,7 +13325,11 @@
           <t>Actually, can you find me one that offers free wifi and parking that has a 2-star rating? I prefer the north area still.</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11737,7 +13341,11 @@
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
-      <c r="J282" s="2" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -11765,7 +13373,11 @@
           <t>I would like to go to a cinema in the area you recommend please.</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11805,7 +13417,11 @@
           <t>I really just need to leave after 15:45. The arrival time doesn't really matter.</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11845,7 +13461,11 @@
           <t>Yes, can you find out if any of them have an opening at 11:45 on Wednesday for 6 people?</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11885,7 +13505,11 @@
           <t>yes and I need a confirmation number</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11925,7 +13549,11 @@
           <t>do they have enough parking?</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -11965,7 +13593,11 @@
           <t>Could you give me the address and phone number for the Slug and Lettuce please.</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12005,7 +13637,11 @@
           <t>Yes, what are my three choices before we make a reservation?</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12017,7 +13653,11 @@
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
-      <c r="J289" s="2" t="inlineStr"/>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -12045,7 +13685,11 @@
           <t>No reservation necessary, just let me know what area of town its in and I'll do the rest.</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12085,7 +13729,11 @@
           <t>No thank you, that is all I needed!</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12125,7 +13773,11 @@
           <t>I also need a taxi between the two places that leaves the hotel by 17:15, please.</t>
         </is>
       </c>
-      <c r="F292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12137,7 +13789,11 @@
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
-      <c r="J292" s="2" t="inlineStr"/>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -12165,7 +13821,11 @@
           <t>No, that's all. thank you!</t>
         </is>
       </c>
-      <c r="F293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12205,7 +13865,11 @@
           <t>I am looking to arrive by 17:15 on tuesday.</t>
         </is>
       </c>
-      <c r="F294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12217,7 +13881,11 @@
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
-      <c r="J294" s="2" t="inlineStr"/>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -12245,7 +13913,11 @@
           <t>OK, that's all that I need. Thank you for being so helpful!</t>
         </is>
       </c>
-      <c r="F295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12285,7 +13957,11 @@
           <t>It should be cheap and include free parking.</t>
         </is>
       </c>
-      <c r="F296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12325,7 +14001,11 @@
           <t>Thanks, I just searched online for it, looks great, please book me for 8 people, 3 nights starting Tuesday.</t>
         </is>
       </c>
-      <c r="F297" s="2" t="inlineStr"/>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12337,7 +14017,11 @@
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr"/>
-      <c r="J297" s="2" t="inlineStr"/>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -12365,7 +14049,11 @@
           <t>Yes. I want the address, postcode and phone number.</t>
         </is>
       </c>
-      <c r="F298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12405,7 +14093,11 @@
           <t>No, that was everything I needed. Thank You!</t>
         </is>
       </c>
-      <c r="F299" s="2" t="inlineStr"/>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12445,7 +14137,11 @@
           <t>The same day.</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12457,7 +14153,11 @@
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr"/>
-      <c r="J300" s="2" t="inlineStr"/>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -12485,7 +14185,11 @@
           <t>It's just me. I am arriving Sunday and staying one night. Can you provide the phone number for the restaurant?</t>
         </is>
       </c>
-      <c r="F301" s="2" t="inlineStr"/>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12497,7 +14201,11 @@
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
-      <c r="J301" s="2" t="inlineStr"/>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -12525,7 +14233,11 @@
           <t>ok thank you good bye</t>
         </is>
       </c>
-      <c r="F302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12565,7 +14277,11 @@
           <t>How about a cheap indian restaurant located in the north please.</t>
         </is>
       </c>
-      <c r="F303" s="2" t="inlineStr"/>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12577,7 +14293,11 @@
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
-      <c r="J303" s="2" t="inlineStr"/>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -12605,7 +14325,11 @@
           <t>Yes, I would like an expensive restaurant that serves Indian food.</t>
         </is>
       </c>
-      <c r="F304" s="2" t="inlineStr"/>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12617,7 +14341,11 @@
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
-      <c r="J304" s="2" t="inlineStr"/>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -12645,7 +14373,11 @@
           <t>I am also looking for a expensive restaurant that serves south african food.</t>
         </is>
       </c>
-      <c r="F305" s="2" t="inlineStr"/>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12657,7 +14389,11 @@
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr"/>
-      <c r="J305" s="2" t="inlineStr"/>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -12685,7 +14421,11 @@
           <t>That is perfect can you book that for me please.</t>
         </is>
       </c>
-      <c r="F306" s="2" t="inlineStr"/>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12697,7 +14437,11 @@
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr"/>
-      <c r="J306" s="2" t="inlineStr"/>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -12725,7 +14469,11 @@
           <t>I will be leaving from Cambridge.</t>
         </is>
       </c>
-      <c r="F307" s="2" t="inlineStr"/>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12737,7 +14485,11 @@
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr"/>
-      <c r="J307" s="2" t="inlineStr"/>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -12765,7 +14517,11 @@
           <t>I need to leave after 17:00.</t>
         </is>
       </c>
-      <c r="F308" s="2" t="inlineStr"/>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12805,7 +14561,11 @@
           <t>Well, could you look for a college?</t>
         </is>
       </c>
-      <c r="F309" s="2" t="inlineStr"/>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12845,7 +14605,11 @@
           <t>Thank you, I appreciate it. I also need some help finding an African restaurant.</t>
         </is>
       </c>
-      <c r="F310" s="2" t="inlineStr"/>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12857,7 +14621,11 @@
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr"/>
-      <c r="J310" s="2" t="inlineStr"/>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -12885,7 +14653,11 @@
           <t>Thanks! I'm also looking for an architecture type place in the west. Can you help me?</t>
         </is>
       </c>
-      <c r="F311" s="2" t="inlineStr"/>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12897,7 +14669,11 @@
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
-      <c r="J311" s="2" t="inlineStr"/>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/4).</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -12925,7 +14701,11 @@
           <t>That's it thanks!</t>
         </is>
       </c>
-      <c r="F312" s="2" t="inlineStr"/>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -12965,7 +14745,11 @@
           <t>Just one ticket, please.</t>
         </is>
       </c>
-      <c r="F313" s="2" t="inlineStr"/>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13005,7 +14789,11 @@
           <t>Great. I was also interested in getting a taxi, can you help me with that?</t>
         </is>
       </c>
-      <c r="F314" s="2" t="inlineStr"/>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13045,7 +14833,11 @@
           <t>i want to leave on monday and arrive by 8</t>
         </is>
       </c>
-      <c r="F315" s="2" t="inlineStr"/>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13085,7 +14877,11 @@
           <t>I am looking to depart cambridge, head to ely, and arrive by 18:30</t>
         </is>
       </c>
-      <c r="F316" s="2" t="inlineStr"/>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13097,7 +14893,11 @@
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
-      <c r="J316" s="2" t="inlineStr"/>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -13125,7 +14925,11 @@
           <t>I need the phone number, postcode, and address.</t>
         </is>
       </c>
-      <c r="F317" s="2" t="inlineStr"/>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13165,7 +14969,11 @@
           <t>Can I get the price range for the restaurant?</t>
         </is>
       </c>
-      <c r="F318" s="2" t="inlineStr"/>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13205,7 +15013,11 @@
           <t>Maybe we can do a picnic in the park. Can you tell me about what's available?</t>
         </is>
       </c>
-      <c r="F319" s="2" t="inlineStr"/>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13245,7 +15057,11 @@
           <t>I'm sorry, could I get the postcode to Cambridge Artworks?</t>
         </is>
       </c>
-      <c r="F320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13285,7 +15101,11 @@
           <t>I need to get to restaurant two two</t>
         </is>
       </c>
-      <c r="F321" s="2" t="inlineStr"/>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13297,7 +15117,11 @@
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
-      <c r="J321" s="2" t="inlineStr"/>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -13325,7 +15149,11 @@
           <t>No thank you. Can you provide me with their phone number?</t>
         </is>
       </c>
-      <c r="F322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13365,7 +15193,11 @@
           <t>Sounds good. Can I get the phone number and postcode?</t>
         </is>
       </c>
-      <c r="F323" s="2" t="inlineStr"/>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13377,7 +15209,11 @@
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr"/>
-      <c r="J323" s="2" t="inlineStr"/>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -13405,7 +15241,11 @@
           <t>Yes, this will be for one person only. Thank you very much</t>
         </is>
       </c>
-      <c r="F324" s="2" t="inlineStr"/>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13445,7 +15285,11 @@
           <t>Yes, please. Either one sounds perfect!</t>
         </is>
       </c>
-      <c r="F325" s="2" t="inlineStr"/>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13457,7 +15301,11 @@
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr"/>
-      <c r="J325" s="2" t="inlineStr"/>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -13485,7 +15333,11 @@
           <t>I need a reference number for that booking!</t>
         </is>
       </c>
-      <c r="F326" s="2" t="inlineStr"/>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13497,7 +15349,11 @@
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr"/>
-      <c r="J326" s="2" t="inlineStr"/>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -13525,7 +15381,11 @@
           <t>Any area is fine I just need info for anyplace where a booking is available.</t>
         </is>
       </c>
-      <c r="F327" s="2" t="inlineStr"/>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13537,7 +15397,11 @@
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr"/>
-      <c r="J327" s="2" t="inlineStr"/>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -13565,7 +15429,11 @@
           <t>Yes, and their address.</t>
         </is>
       </c>
-      <c r="F328" s="2" t="inlineStr"/>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13605,7 +15473,11 @@
           <t>Yes please book it for 8 people and give me the reference number</t>
         </is>
       </c>
-      <c r="F329" s="2" t="inlineStr"/>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13617,7 +15489,11 @@
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr"/>
-      <c r="J329" s="2" t="inlineStr"/>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -13645,7 +15521,11 @@
           <t>Thanks. I also need train information for Wednesday with an arrival by 16:15.</t>
         </is>
       </c>
-      <c r="F330" s="2" t="inlineStr"/>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13657,7 +15537,11 @@
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr"/>
-      <c r="J330" s="2" t="inlineStr"/>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -13685,7 +15569,11 @@
           <t>Yes, please. 7 people at 18:30 on tuesday.</t>
         </is>
       </c>
-      <c r="F331" s="2" t="inlineStr"/>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13697,7 +15585,11 @@
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr"/>
-      <c r="J331" s="2" t="inlineStr"/>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -13725,7 +15617,11 @@
           <t>I would like a guesthouse with free parking and a 4 star rating.</t>
         </is>
       </c>
-      <c r="F332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13765,7 +15661,11 @@
           <t>What time does it depart?</t>
         </is>
       </c>
-      <c r="F333" s="2" t="inlineStr"/>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13777,7 +15677,11 @@
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
-      <c r="J333" s="2" t="inlineStr"/>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -13805,7 +15709,11 @@
           <t>Thank you very much. that should be all.</t>
         </is>
       </c>
-      <c r="F334" s="2" t="inlineStr"/>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13845,7 +15753,11 @@
           <t>No, I believe that is everything. Thank you.</t>
         </is>
       </c>
-      <c r="F335" s="2" t="inlineStr"/>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13885,7 +15797,11 @@
           <t>Can you give me the address, price range, and phone number of the best one?</t>
         </is>
       </c>
-      <c r="F336" s="2" t="inlineStr"/>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13925,7 +15841,11 @@
           <t>Are there any museums nearby?</t>
         </is>
       </c>
-      <c r="F337" s="2" t="inlineStr"/>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13965,7 +15885,11 @@
           <t>Well I'm also looking for a train. Can you coordinate a time with a departure from cambride on sunday?</t>
         </is>
       </c>
-      <c r="F338" s="2" t="inlineStr"/>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -13977,7 +15901,11 @@
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr"/>
-      <c r="J338" s="2" t="inlineStr"/>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -14005,7 +15933,11 @@
           <t>No thank you, not at this time. Could you tell me the price?</t>
         </is>
       </c>
-      <c r="F339" s="2" t="inlineStr"/>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14017,7 +15949,11 @@
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr"/>
-      <c r="J339" s="2" t="inlineStr"/>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=3/0/4/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -14045,7 +15981,11 @@
           <t>Thank you! That is all I need.</t>
         </is>
       </c>
-      <c r="F340" s="2" t="inlineStr"/>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14085,7 +16025,11 @@
           <t>Nope, that'll do it. Thanks for your help!</t>
         </is>
       </c>
-      <c r="F341" s="2" t="inlineStr"/>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14125,7 +16069,11 @@
           <t>Thanks for handling the restaurant. I will have time to check out the town. Do you have multiple sports in the same area as the restaurant?</t>
         </is>
       </c>
-      <c r="F342" s="2" t="inlineStr"/>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14137,7 +16085,11 @@
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr"/>
-      <c r="J342" s="2" t="inlineStr"/>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -14165,7 +16117,11 @@
           <t>yes please. book it for 3 people and 3 nights starting from friday.</t>
         </is>
       </c>
-      <c r="F343" s="2" t="inlineStr"/>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14177,7 +16133,11 @@
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr"/>
-      <c r="J343" s="2" t="inlineStr"/>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -14205,7 +16165,11 @@
           <t>What about cheap 4 star hotels?</t>
         </is>
       </c>
-      <c r="F344" s="2" t="inlineStr"/>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14217,7 +16181,11 @@
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr"/>
-      <c r="J344" s="2" t="inlineStr"/>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -14245,7 +16213,11 @@
           <t>Yes, I am looking in the expensive price range. Also, I would need free parking.</t>
         </is>
       </c>
-      <c r="F345" s="2" t="inlineStr"/>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14257,7 +16229,11 @@
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr"/>
-      <c r="J345" s="2" t="inlineStr"/>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -14285,7 +16261,11 @@
           <t>Thank you! Are there any guesthouses nearby?</t>
         </is>
       </c>
-      <c r="F346" s="2" t="inlineStr"/>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14297,7 +16277,11 @@
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr"/>
-      <c r="J346" s="2" t="inlineStr"/>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -14325,7 +16309,11 @@
           <t>Sure, is there a nightclub in that part of town?</t>
         </is>
       </c>
-      <c r="F347" s="2" t="inlineStr"/>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14337,7 +16325,11 @@
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr"/>
-      <c r="J347" s="2" t="inlineStr"/>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -14365,7 +16357,11 @@
           <t>Whenever is fine, just for me.</t>
         </is>
       </c>
-      <c r="F348" s="2" t="inlineStr"/>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14405,7 +16401,11 @@
           <t>Can you pick one for me?</t>
         </is>
       </c>
-      <c r="F349" s="2" t="inlineStr"/>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14445,7 +16445,11 @@
           <t>Are there any good cheap places to eat in the same area?</t>
         </is>
       </c>
-      <c r="F350" s="2" t="inlineStr"/>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14457,7 +16461,11 @@
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr"/>
-      <c r="J350" s="2" t="inlineStr"/>
+      <c r="J350" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -14485,7 +16493,11 @@
           <t>Thank you. That's all I need.</t>
         </is>
       </c>
-      <c r="F351" s="2" t="inlineStr"/>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14612,7 +16624,11 @@
           <t>I would like to leave on Wednesday and the train should leave after 09:00.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14656,7 +16672,11 @@
           <t>Can you try another hotel in the same price range?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14700,7 +16720,11 @@
           <t>Yes I also need a taxi to commute between the two.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14744,7 +16768,11 @@
           <t>Can you help me find a train going to Stevenage and leaving Thursday instead?</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14760,7 +16788,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -14788,7 +16820,11 @@
           <t>Can I get the postal code for that hotel?</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14832,7 +16868,11 @@
           <t>That's leaving from Cambridge, right? If so, then yes, book me one seat, and give me the reference number, thanks!</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14848,7 +16888,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -14876,7 +16920,11 @@
           <t>Please have a taxi take me from my hotel to the restaurant, arriving in time for my reservation. And give me the booking info</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14892,7 +16940,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -14920,7 +16972,11 @@
           <t>Sure! Which one do you recommend?</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14964,7 +17020,11 @@
           <t>Yes! I would also like to book a taxi.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -14980,7 +17040,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -15008,7 +17072,11 @@
           <t>No, that'll be all. Thank you, again.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15052,7 +17120,11 @@
           <t>Yes, please make reservations for 5 people at 16:45 on Monday.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15068,7 +17140,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -15096,7 +17172,11 @@
           <t>Yes, i am looking for places to visit on the east side of town.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15112,7 +17192,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/0).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -15140,7 +17224,11 @@
           <t>I want one that serves light bites.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15156,7 +17244,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -15184,7 +17276,11 @@
           <t>Can you try another restaurant?</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15228,7 +17324,11 @@
           <t>I'm good, thanks for your help!</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15272,7 +17372,11 @@
           <t>On second thought I just wanted to find a hotel in the south area. Thanks so much for your help!</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15316,7 +17420,11 @@
           <t>May I have the phone number for the park please?</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15360,7 +17468,11 @@
           <t>I want to book 3 nights there, please.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15376,7 +17488,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -15404,7 +17520,11 @@
           <t>I need something moderately priced in the centre. What would you recommend?</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15448,7 +17568,11 @@
           <t>What's the postcode and enterance fee?</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15492,7 +17616,11 @@
           <t>I prefer the eastern part of town and something that is 4-star rated.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15508,7 +17636,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15536,7 +17668,11 @@
           <t>It doesn't really matter. Can you recommend one?</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15580,7 +17716,11 @@
           <t>I would like the one closest to the alexander bed and breakfast please.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15624,7 +17764,11 @@
           <t>Three stars, moderate price range.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15668,7 +17812,11 @@
           <t>I would like to be in the south and I prefer a guesthouse.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15684,7 +17832,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15712,7 +17864,11 @@
           <t>What is the postcode of that resturant?</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15756,7 +17912,11 @@
           <t>How about the bridge guest house for 5 people for 2 nights starting on tuesday?</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15800,7 +17960,11 @@
           <t>I would like to leave Wednesday after 20:00.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15844,7 +18008,11 @@
           <t>Yes, that will work.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15888,7 +18056,11 @@
           <t>I also need the area and address of an attraction called Old Schools please.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15904,7 +18076,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -15932,7 +18108,11 @@
           <t>It does not really matter can you suggest one?</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15976,7 +18156,11 @@
           <t>uhm, no. that's your job, weirdo. also, i need a train.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT_CLARIFY</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -15992,7 +18176,11 @@
           <t>dhiraajd</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -16020,7 +18208,11 @@
           <t>I'm sorry, I just needed the train info. However, I need a place to stay in the North preferably with parking. Can you assist?</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16064,7 +18256,11 @@
           <t>How about british food?</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16108,7 +18304,11 @@
           <t>Thank you. That is all I need.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16152,7 +18352,11 @@
           <t>OK, that sounds great. I also need a train to get me to Cambridge.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRM_ACCEPT</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16196,7 +18400,11 @@
           <t>I'll be going to Cambridge on Saturday.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16240,7 +18448,11 @@
           <t>No that's all for today, thank you.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16284,7 +18496,11 @@
           <t>What is the star of the hotel?</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16328,7 +18544,11 @@
           <t>I don't know the city, so I don't really care about the location within town. Can you recommend an area?</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16372,7 +18592,11 @@
           <t>Let's go with that. What's the address?</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16416,7 +18640,11 @@
           <t>Departure time doesn't matter, I just want to arrive by 17:00 Monday.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16460,7 +18688,11 @@
           <t>I think that will do it. Thanks for the information.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>SOCIAL</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16504,7 +18736,11 @@
           <t>Great I also need a taxi that will leave the attraction by 16:15</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>INFORM_CONSTRAINT</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>
@@ -16548,7 +18784,11 @@
           <t>What about Italian food?</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>adesanym</t>

--- a/annotation/excel/adesanym_annotation.xlsx
+++ b/annotation/excel/adesanym_annotation.xlsx
@@ -543,7 +543,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/0/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT, SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/0).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/0/0/4).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8575,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected SOCIAL via tie break order (scores C/A/R/I/S=0/0/2/2/4).</t>
+          <t>Ambiguous mixed intent; selected SOCIAL via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -9671,7 +9671,7 @@
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       <c r="I213" s="2" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
       <c r="I220" s="2" t="inlineStr"/>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10535,7 @@
       <c r="I221" s="2" t="inlineStr"/>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       <c r="I222" s="2" t="inlineStr"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       <c r="I223" s="2" t="inlineStr"/>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
       <c r="I226" s="2" t="inlineStr"/>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       <c r="I232" s="2" t="inlineStr"/>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       <c r="I233" s="2" t="inlineStr"/>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
       <c r="I238" s="2" t="inlineStr"/>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       <c r="I240" s="2" t="inlineStr"/>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=3/0/4/0/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CORRECT_CLARIFY.</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       <c r="I242" s="2" t="inlineStr"/>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       <c r="I247" s="2" t="inlineStr"/>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       <c r="I248" s="2" t="inlineStr"/>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       <c r="I253" s="2" t="inlineStr"/>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12043,7 +12043,7 @@
       <c r="I254" s="2" t="inlineStr"/>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       <c r="I255" s="2" t="inlineStr"/>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/0/4).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST, SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       <c r="I256" s="2" t="inlineStr"/>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12323,7 @@
       <c r="I260" s="2" t="inlineStr"/>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/0/2/4).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
       <c r="I261" s="2" t="inlineStr"/>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       <c r="I263" s="2" t="inlineStr"/>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/0/4).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       <c r="I264" s="2" t="inlineStr"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       <c r="I265" s="2" t="inlineStr"/>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       <c r="I266" s="2" t="inlineStr"/>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       <c r="I268" s="2" t="inlineStr"/>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
       <c r="I270" s="2" t="inlineStr"/>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       <c r="I273" s="2" t="inlineStr"/>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12975,7 @@
       <c r="I274" s="2" t="inlineStr"/>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       <c r="I275" s="2" t="inlineStr"/>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -13071,7 +13071,7 @@
       <c r="I276" s="2" t="inlineStr"/>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       <c r="I278" s="2" t="inlineStr"/>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
       <c r="I282" s="2" t="inlineStr"/>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13655,7 @@
       <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       <c r="I292" s="2" t="inlineStr"/>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -13883,7 +13883,7 @@
       <c r="I294" s="2" t="inlineStr"/>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       <c r="I297" s="2" t="inlineStr"/>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       <c r="I300" s="2" t="inlineStr"/>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       <c r="I301" s="2" t="inlineStr"/>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
       <c r="I304" s="2" t="inlineStr"/>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       <c r="I305" s="2" t="inlineStr"/>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14439,7 +14439,7 @@
       <c r="I306" s="2" t="inlineStr"/>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -14487,7 +14487,7 @@
       <c r="I307" s="2" t="inlineStr"/>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -14623,7 +14623,7 @@
       <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       <c r="I311" s="2" t="inlineStr"/>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/4).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       <c r="I316" s="2" t="inlineStr"/>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       <c r="I321" s="2" t="inlineStr"/>
       <c r="J321" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       <c r="I323" s="2" t="inlineStr"/>
       <c r="J323" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15351,7 @@
       <c r="I326" s="2" t="inlineStr"/>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15399,7 +15399,7 @@
       <c r="I327" s="2" t="inlineStr"/>
       <c r="J327" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       <c r="I329" s="2" t="inlineStr"/>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
       <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
       <c r="I331" s="2" t="inlineStr"/>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       <c r="I333" s="2" t="inlineStr"/>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/0).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
       <c r="I338" s="2" t="inlineStr"/>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -15951,7 +15951,7 @@
       <c r="I339" s="2" t="inlineStr"/>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=3/0/4/2/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CORRECT_CLARIFY.</t>
         </is>
       </c>
     </row>
@@ -16087,7 +16087,7 @@
       <c r="I342" s="2" t="inlineStr"/>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT, SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16135,7 @@
       <c r="I343" s="2" t="inlineStr"/>
       <c r="J343" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -16183,7 +16183,7 @@
       <c r="I344" s="2" t="inlineStr"/>
       <c r="J344" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -16231,7 +16231,7 @@
       <c r="I345" s="2" t="inlineStr"/>
       <c r="J345" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -16279,7 +16279,7 @@
       <c r="I346" s="2" t="inlineStr"/>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
       <c r="I347" s="2" t="inlineStr"/>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       <c r="I350" s="2" t="inlineStr"/>
       <c r="J350" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=4/0/4/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/2/4/0/2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST.</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -17194,7 +17194,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/0/2/0).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/0).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17490,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order (scores C/A/R/I/S=0/2/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected CONFIRM_ACCEPT via tie break order. Also considered: REQUEST, INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order (scores C/A/R/I/S=0/0/0/2/2).</t>
+          <t>Ambiguous mixed intent; selected INFORM_CONSTRAINT via tie break order. Also considered: SOCIAL.</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17834,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected REQUEST via tie break order (scores C/A/R/I/S=0/0/2/2/-2).</t>
+          <t>Ambiguous mixed intent; selected REQUEST via tie break order. Also considered: INFORM_CONSTRAINT.</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order (scores C/A/R/I/S=0/0/0/0/-2).</t>
+          <t>Ambiguous mixed intent; selected CORRECT_CLARIFY via tie break order. Also considered: CONFIRM_ACCEPT.</t>
         </is>
       </c>
     </row>
